--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.2788962756752</v>
+        <v>4.10782064479722</v>
       </c>
       <c r="D2" t="n">
-        <v>25.23262614760384</v>
+        <v>4.100301748985625</v>
       </c>
       <c r="E2" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F2" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.99875635181146</v>
+        <v>5.199797907169363</v>
       </c>
       <c r="D3" t="n">
-        <v>31.48925877299917</v>
+        <v>5.117004550612365</v>
       </c>
       <c r="E3" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F3" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.38490556188653</v>
+        <v>2.987547153806561</v>
       </c>
       <c r="D4" t="n">
-        <v>18.3664387975941</v>
+        <v>2.984546304609041</v>
       </c>
       <c r="E4" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F4" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.5916501781952</v>
+        <v>8.221143153956719</v>
       </c>
       <c r="D5" t="n">
-        <v>64.98418537981132</v>
+        <v>10.55993012421934</v>
       </c>
       <c r="E5" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F5" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.19856817811307</v>
+        <v>2.307267328943373</v>
       </c>
       <c r="D6" t="n">
-        <v>28.6161860869381</v>
+        <v>4.650130239127441</v>
       </c>
       <c r="E6" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F6" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.96118940925997</v>
+        <v>5.031193279004746</v>
       </c>
       <c r="D7" t="n">
-        <v>31.00074559303057</v>
+        <v>5.037621158867467</v>
       </c>
       <c r="E7" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F7" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.30387283033944</v>
+        <v>4.111879334930158</v>
       </c>
       <c r="D8" t="n">
-        <v>25.32760962631631</v>
+        <v>4.115736564276401</v>
       </c>
       <c r="E8" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F8" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.088161496957233</v>
+        <v>1.15182624325555</v>
       </c>
       <c r="D9" t="n">
-        <v>8.276596556045101</v>
+        <v>1.344946940357329</v>
       </c>
       <c r="E9" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F9" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.17960348286838</v>
+        <v>5.391685565966112</v>
       </c>
       <c r="D10" t="n">
-        <v>33.17920853693192</v>
+        <v>5.391621387251437</v>
       </c>
       <c r="E10" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F10" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>54.19596193437958</v>
+        <v>8.806843814336681</v>
       </c>
       <c r="D11" t="n">
-        <v>54.2059813095024</v>
+        <v>8.80847196279414</v>
       </c>
       <c r="E11" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F11" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>59.2532056456397</v>
+        <v>9.628645917416451</v>
       </c>
       <c r="D12" t="n">
-        <v>59.27304975264862</v>
+        <v>9.6318705848054</v>
       </c>
       <c r="E12" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F12" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.13010639783543</v>
+        <v>5.383642289648257</v>
       </c>
       <c r="D13" t="n">
-        <v>33.01247029834033</v>
+        <v>5.364526423480303</v>
       </c>
       <c r="E13" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F13" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.15913001809416</v>
+        <v>2.950858627940302</v>
       </c>
       <c r="D14" t="n">
-        <v>18.1828183850527</v>
+        <v>2.954707987571064</v>
       </c>
       <c r="E14" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F14" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>78.00396824139408</v>
+        <v>12.67564483922654</v>
       </c>
       <c r="D15" t="n">
-        <v>78.14760768486779</v>
+        <v>12.69898624879102</v>
       </c>
       <c r="E15" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F15" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.5276573993307</v>
+        <v>7.073244327391239</v>
       </c>
       <c r="D16" t="n">
-        <v>43.66983890385927</v>
+        <v>7.096348821877131</v>
       </c>
       <c r="E16" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F16" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>70.67002228058973</v>
+        <v>11.48387862059583</v>
       </c>
       <c r="D17" t="n">
-        <v>70.81447671389701</v>
+        <v>11.50735246600826</v>
       </c>
       <c r="E17" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F17" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.45171655970808</v>
+        <v>6.898403940952564</v>
       </c>
       <c r="D18" t="n">
-        <v>42.41679286474572</v>
+        <v>6.892728840521181</v>
       </c>
       <c r="E18" t="n">
-        <v>19.31339582557393</v>
+        <v>3.138426821655762</v>
       </c>
       <c r="F18" t="n">
-        <v>19.36101261576566</v>
+        <v>3.14616455006192</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
